--- a/Assets/Resources/DataFiles/RestData/1. ExcelFile/RestData.xlsx
+++ b/Assets/Resources/DataFiles/RestData/1. ExcelFile/RestData.xlsx
@@ -436,12 +436,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>creditPerHealthPoint</t>
+          <t>creditPerAct</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>creditPerPotionCharge</t>
+          <t>potionRechargeAmount</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -457,17 +457,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>캠프 휴식 기본값. baseHealPercent=캠프 회복 증가 패시브 미해금 시 최대 체력 대비 회복 비율(%), 해금 시에는 패시브 수치(40%)를 대신 사용. creditPerHealthPoint=체력 1 회복당 크레딧, creditPerPotionCharge=포션 1충전당 크레딧.</t>
+          <t>캠프 휴식 기본값. baseHealPercent=캠프 회복 증가 패시브 미해금 시 최대 체력 대비 회복 비율(%), 해금 시에는 패시브 수치(40%)를 대신 사용. creditPerAct=휴식 1회 비용(× 현재 액트 번호, Act1=500/Act2=1000/Act3=1500), potionRechargeAmount=휴식 1회로 채우는 포션 충전 수(최대 충전량까지만). 회복할 체력·포션이 없으면 비용을 받지 않는다.</t>
         </is>
       </c>
     </row>
